--- a/outputs/9448.xlsx
+++ b/outputs/9448.xlsx
@@ -188,7 +188,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,###"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="169" formatCode="@"/>
     <numFmt numFmtId="170" formatCode="m/d/yy\ h:mm\ AM/PM"/>
   </numFmts>
@@ -537,128 +537,132 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -682,15 +686,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -989,764 +993,764 @@
   <dimension ref="A1:U18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="8.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="9.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="9.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="8.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.31"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="G6" s="16" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11"/>
+      <c r="G6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="13" t="n">
+      <c r="H6" s="18"/>
+      <c r="I6" s="14" t="n">
         <v>2015</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="18" t="n">
+      <c r="J6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="19" t="n">
         <v>2016</v>
       </c>
-      <c r="Q6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="15" t="s">
+      <c r="Q6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="G7" s="19" t="s">
+      <c r="A7" s="11"/>
+      <c r="G7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21" t="s">
+      <c r="H7" s="21"/>
+      <c r="I7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="K7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="22" t="s">
+      <c r="O7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="P7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="22" t="s">
+      <c r="Q7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="22" t="s">
+      <c r="R7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="22" t="s">
+      <c r="S7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T7" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28" t="n">
+      <c r="H8" s="28"/>
+      <c r="I8" s="29" t="n">
         <f aca="false">SUM(I9:I18)</f>
         <v>6</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <f aca="false">SUM(J9:J18)</f>
         <v>3</v>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="29" t="n">
         <f aca="false">SUM(K9:K18)</f>
         <v>3</v>
       </c>
-      <c r="L8" s="28" t="n">
+      <c r="L8" s="29" t="n">
         <f aca="false">SUM(L9:L18)</f>
         <v>2</v>
       </c>
-      <c r="M8" s="28" t="n">
+      <c r="M8" s="29" t="n">
         <f aca="false">SUM(M9:M18)</f>
         <v>3</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="29" t="n">
         <f aca="false">SUM(N9:N18)</f>
         <v>3</v>
       </c>
-      <c r="O8" s="28" t="n">
+      <c r="O8" s="29" t="n">
         <f aca="false">SUM(O9:O18)</f>
         <v>2</v>
       </c>
-      <c r="P8" s="28" t="n">
+      <c r="P8" s="29" t="n">
         <f aca="false">SUM(P9:P18)</f>
         <v>8</v>
       </c>
-      <c r="Q8" s="28" t="n">
+      <c r="Q8" s="29" t="n">
         <f aca="false">SUM(Q9:Q18)</f>
         <v>2</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="R8" s="29" t="n">
         <f aca="false">SUM(R9:R18)</f>
         <v>2</v>
       </c>
-      <c r="S8" s="28" t="n">
+      <c r="S8" s="29" t="n">
         <f aca="false">SUM(S9:S18)</f>
         <v>2</v>
       </c>
-      <c r="T8" s="28" t="n">
+      <c r="T8" s="29" t="n">
         <f aca="false">SUM(T9:T18)</f>
         <v>0</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="U8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="s">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="35"/>
-      <c r="U9" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I9:T9&gt;0),COLUMN(I9:T9))-9)</f>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="36"/>
+      <c r="U9" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I9:T9&lt;&gt;""),COLUMN(I9:T9))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I9:T9&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42461</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="31" t="n">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I10:T10&gt;0),COLUMN(I10:T10))-9)</f>
+      <c r="I10" s="33"/>
+      <c r="J10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I10:T10&lt;&gt;""),COLUMN(I10:T10))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I10:T10&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42186</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="31" t="n">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I11:T11&gt;0),COLUMN(I11:T11))-9)</f>
+      <c r="I11" s="33"/>
+      <c r="J11" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I11:T11&lt;&gt;""),COLUMN(I11:T11))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I11:T11&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42217</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="31" t="n">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I12:T12&gt;0),COLUMN(I12:T12))-9)</f>
+      <c r="I12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I12:T12&lt;&gt;""),COLUMN(I12:T12))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I12:T12&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42370</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="31" t="n">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="39" t="n">
+      <c r="I13" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="34" t="n">
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I13:T13&gt;0),COLUMN(I13:T13))-9)</f>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I13:T13&lt;&gt;""),COLUMN(I13:T13))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I13:T13&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42370</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="31" t="n">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="39" t="n">
+      <c r="I14" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="33"/>
-      <c r="K14" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="34" t="n">
+      <c r="J14" s="34"/>
+      <c r="K14" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="O14" s="33"/>
-      <c r="P14" s="34" t="n">
+      <c r="O14" s="34"/>
+      <c r="P14" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I14:T14&gt;0),COLUMN(I14:T14))-9)</f>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I14:T14&lt;&gt;""),COLUMN(I14:T14))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I14:T14&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42370</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="31" t="n">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="39" t="n">
+      <c r="I15" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I15:T15&gt;0),COLUMN(I15:T15))-9)</f>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I15:T15&lt;&gt;""),COLUMN(I15:T15))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I15:T15&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42401</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="31" t="n">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="33"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I16:T16&gt;0),COLUMN(I16:T16))-9)</f>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="34"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I16:T16&lt;&gt;""),COLUMN(I16:T16))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I16:T16&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42430</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="31" t="n">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I17:T17&gt;0),COLUMN(I17:T17))-9)</f>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I17:T17&lt;&gt;""),COLUMN(I17:T17))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I17:T17&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42278</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="31" t="n">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="34" t="n">
+      <c r="I18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="33"/>
-      <c r="S18" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="35"/>
-      <c r="U18" s="36" t="n">
-        <f aca="false">EDATE(DATE(2015,6,1),LOOKUP(2,1/(I18:T18&gt;0),COLUMN(I18:T18))-9)</f>
+      <c r="R18" s="34"/>
+      <c r="S18" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="36"/>
+      <c r="U18" s="37" t="n">
+        <f aca="false">DATE(IF(LOOKUP(2,1/(I18:T18&lt;&gt;""),COLUMN(I18:T18))&lt;=15,2015,2016),MATCH(LOOKUP(2,1/(I18:T18&lt;&gt;""),$I$7:$T$7),{"January","February","March","April","May","June","July","August","September","October","November","December"},0),1)</f>
         <v>42461</v>
       </c>
     </row>
@@ -1769,111 +1773,111 @@
   <dimension ref="A2:I19"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="1" style="40" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="40" width="16.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="40" width="9.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="1" style="41" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="41" width="16.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="41" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="43" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44" t="s">
+      <c r="F7" s="45"/>
+      <c r="G7" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="47"/>
+      <c r="E8" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47" t="n">
+      <c r="F8" s="47"/>
+      <c r="G8" s="48" t="n">
         <v>42537.5054050926</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44" t="s">
+      <c r="D12" s="45"/>
+      <c r="E12" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="46" t="s">
+      <c r="B13" s="46"/>
+      <c r="C13" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46" t="s">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="48" t="s">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="49" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40" t="s">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="41" t="s">
         <v>51</v>
       </c>
     </row>
